--- a/Comparisons.xlsx
+++ b/Comparisons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FrancescoP\ImagingBased-ProgressionPrediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{799EF021-FBA7-4581-983A-86D5E80FBBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29733014-D1E7-4152-B626-3C1CA529FD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2EE0F8F3-7531-4A73-A202-515B415B47BD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="96">
   <si>
     <t>Slope distribution</t>
   </si>
@@ -248,14 +248,89 @@
     <t>Training 2 (MSE)</t>
   </si>
   <si>
-    <t>Training 3 (Huber)</t>
+    <t xml:space="preserve">Training 4 - Huber , slopes  normalization, no attention, weight sampling </t>
+  </si>
+  <si>
+    <t>249.06 ± 37.61</t>
+  </si>
+  <si>
+    <t>334.77 ± 47.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.8290 ± 0.0642</t>
+  </si>
+  <si>
+    <t>0.517 ± 0.098</t>
+  </si>
+  <si>
+    <t>0.691 ± 0.183</t>
+  </si>
+  <si>
+    <t>0.342 ± 0.200</t>
+  </si>
+  <si>
+    <t>0.418 ± 0.183</t>
+  </si>
+  <si>
+    <t>0.761 ± 0.168</t>
+  </si>
+  <si>
+    <t>0.560 ± 0.114</t>
+  </si>
+  <si>
+    <t>0.658 ± 0.129</t>
+  </si>
+  <si>
+    <t>Training 3 (Huber-no norm)</t>
+  </si>
+  <si>
+    <t>Training 4 (Huber)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training 5 - MSE , slopes no normalization, attention, weight sampling </t>
+  </si>
+  <si>
+    <t>249.26 ± 32.75</t>
+  </si>
+  <si>
+    <t>333.93 ± 45.43</t>
+  </si>
+  <si>
+    <t>0.8301 ± 0.0616</t>
+  </si>
+  <si>
+    <t>0.517 ± 0.084</t>
+  </si>
+  <si>
+    <t>0.770 ± 0.196</t>
+  </si>
+  <si>
+    <t>0.365 ± 0.195</t>
+  </si>
+  <si>
+    <t>0.428 ± 0.188</t>
+  </si>
+  <si>
+    <t>0.756 ± 0.208</t>
+  </si>
+  <si>
+    <t>0.546 ± 0.135</t>
+  </si>
+  <si>
+    <t>0.658 ± 0.113</t>
+  </si>
+  <si>
+    <t>Training 5 (MSE-no norm,att)</t>
+  </si>
+  <si>
+    <t>MAE FVC(52)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +342,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -414,55 +495,119 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -536,6 +681,36 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -569,86 +744,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -666,16 +761,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>226616</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>85613</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>522451</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>31824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>484095</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>34655</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>591671</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>160161</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -698,8 +793,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9119604" y="802789"/>
-          <a:ext cx="5985926" cy="3687325"/>
+          <a:off x="9343722" y="31824"/>
+          <a:ext cx="5430114" cy="3687325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -716,8 +811,8 @@
       <xdr:rowOff>89647</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>116394</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>609452</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>125506</xdr:rowOff>
     </xdr:to>
@@ -840,21 +935,110 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>833718</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>17930</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>249795</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>40109</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64E61601-12B0-8B2E-670A-05B9FABFF28A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17508071" y="10031506"/>
+          <a:ext cx="3324689" cy="2353003"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>806825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>107578</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>46012</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>35859</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CDCBCBC-2B09-BE04-73BF-D8F9BA227EA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7512425" y="14603507"/>
+          <a:ext cx="3111940" cy="2259105"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3DAEFBCC-FF40-4F66-B649-0C96AC862806}" name="Table2" displayName="Table2" ref="A25:H28" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
-  <autoFilter ref="A25:H28" xr:uid="{3DAEFBCC-FF40-4F66-B649-0C96AC862806}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1AB4FC38-4517-44F4-A99A-E57AA670AD0F}" name="Training" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{B424091A-0662-4390-A0BE-918C2A0A03FC}" name="Accuracy" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{EB3FD60A-926F-457D-B1BB-C6AA1875C8C0}" name="Precision" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{DD322310-0117-4984-99C0-4E835D410D91}" name="Recall" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E019C0FD-7F71-4FCD-A98E-66D99246B5AB}" name="F1-Score" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{DC66C15B-74CC-4F2B-858F-2B2AA38304B0}" name="Specificity" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3DAEFBCC-FF40-4F66-B649-0C96AC862806}" name="Table2" displayName="Table2" ref="A25:I30" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A25:I30" xr:uid="{3DAEFBCC-FF40-4F66-B649-0C96AC862806}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{1AB4FC38-4517-44F4-A99A-E57AA670AD0F}" name="Training" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B424091A-0662-4390-A0BE-918C2A0A03FC}" name="Accuracy" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{EB3FD60A-926F-457D-B1BB-C6AA1875C8C0}" name="Precision" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{DD322310-0117-4984-99C0-4E835D410D91}" name="Recall" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{E019C0FD-7F71-4FCD-A98E-66D99246B5AB}" name="F1-Score" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{DC66C15B-74CC-4F2B-858F-2B2AA38304B0}" name="Specificity" dataDxfId="4"/>
     <tableColumn id="8" xr3:uid="{47AE70D0-AB50-4496-AFB0-1AD3D4827CA8}" name="AUC"/>
-    <tableColumn id="9" xr3:uid="{45ADE258-6CA2-422A-81B2-1753A5D5207C}" name="AP" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{45ADE258-6CA2-422A-81B2-1753A5D5207C}" name="AP" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{2E69A242-1017-4CBC-88EB-F049FD853CEF}" name="MAE FVC(52)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1177,50 +1361,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F468E34-A5AC-46DE-BB00-B66C779675C6}">
-  <dimension ref="A1:S78"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S103"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.3984375" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14.296875" customWidth="1"/>
-    <col min="4" max="4" width="15.09765625" customWidth="1"/>
-    <col min="5" max="5" width="14.3984375" customWidth="1"/>
-    <col min="6" max="6" width="13.796875" customWidth="1"/>
-    <col min="7" max="7" width="15.3984375" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="11.5" customWidth="1"/>
-    <col min="13" max="13" width="12.296875" customWidth="1"/>
-    <col min="14" max="15" width="12.3984375" customWidth="1"/>
-    <col min="16" max="16" width="11.69921875" customWidth="1"/>
-    <col min="17" max="17" width="12.09765625" customWidth="1"/>
-    <col min="18" max="18" width="12" customWidth="1"/>
-    <col min="19" max="19" width="12.09765625" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" customWidth="1"/>
+    <col min="7" max="8" width="15.44140625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" customWidth="1"/>
+    <col min="19" max="19" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1">
@@ -1232,29 +1416,25 @@
       <c r="D2" s="1">
         <v>6.12</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="8">
         <v>0.14199999999999999</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="6">
         <v>0.78400000000000003</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="1">
@@ -1266,17 +1446,15 @@
       <c r="D4" s="1">
         <v>5.98</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="8">
         <v>0.152</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="6">
         <v>0.752</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B5" s="1">
@@ -1288,17 +1466,15 @@
       <c r="D5" s="1">
         <v>5.18</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="8">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="6">
         <v>0.82899999999999996</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="1">
@@ -1310,29 +1486,25 @@
       <c r="D6" s="1">
         <v>7.19</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="8">
         <v>0.16700000000000001</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="6">
         <v>0.83299999999999996</v>
       </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="1">
@@ -1344,17 +1516,15 @@
       <c r="D8" s="1">
         <v>6.4</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="8">
         <v>0.17</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="6">
         <v>0.78300000000000003</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="1">
@@ -1366,17 +1536,15 @@
       <c r="D9" s="1">
         <v>5.78</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="8">
         <v>0.114</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="6">
         <v>0.77100000000000002</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B10" s="1">
@@ -1388,29 +1556,25 @@
       <c r="D10" s="1">
         <v>5.18</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="8">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="6">
         <v>0.82899999999999996</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="23"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="1">
@@ -1422,17 +1586,15 @@
       <c r="D12" s="1">
         <v>6.16</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="8">
         <v>0.13200000000000001</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="6">
         <v>0.80200000000000005</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="1">
@@ -1444,17 +1606,15 @@
       <c r="D13" s="1">
         <v>5.97</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="8">
         <v>0.2</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="6">
         <v>0.68600000000000005</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="1">
@@ -1466,29 +1626,25 @@
       <c r="D14" s="1">
         <v>5.78</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="8">
         <v>0.114</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="6">
         <v>0.77100000000000002</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="1">
@@ -1500,17 +1656,15 @@
       <c r="D16" s="1">
         <v>6.22</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="8">
         <v>0.123</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="7">
         <v>0.84</v>
       </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="1">
@@ -1522,17 +1676,15 @@
       <c r="D17" s="1">
         <v>5.87</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="8">
         <v>0.14299999999999999</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="6">
         <v>0.71399999999999997</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="1">
@@ -1544,29 +1696,25 @@
       <c r="D18" s="1">
         <v>5.97</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="8">
         <v>0.2</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="6">
         <v>0.68600000000000005</v>
       </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="23"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="1">
@@ -1578,17 +1726,15 @@
       <c r="D20" s="1">
         <v>5.79</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="8">
         <v>0.13300000000000001</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="6">
         <v>0.79</v>
       </c>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="1">
@@ -1600,17 +1746,15 @@
       <c r="D21" s="1">
         <v>7.19</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="8">
         <v>0.16700000000000001</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="6">
         <v>0.83299999999999996</v>
       </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="1">
@@ -1622,82 +1766,90 @@
       <c r="D22" s="1">
         <v>5.87</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="8">
         <v>0.14299999999999999</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="6">
         <v>0.71399999999999997</v>
       </c>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="30" t="s">
+      <c r="G25" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="I25" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="12" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="I26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
         <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1715,112 +1867,174 @@
       <c r="F27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="13" t="s">
+      <c r="I27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="33" t="s">
+      <c r="H28" s="17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="I28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="7" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K34" s="20" t="s">
+      <c r="K34" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20" t="s">
+      <c r="L34" s="10"/>
+      <c r="M34" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N34" s="20" t="s">
+      <c r="N34" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O34" s="20" t="s">
+      <c r="O34" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="P34" s="22" t="s">
+      <c r="P34" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="Q34" s="22" t="s">
+      <c r="Q34" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -1839,10 +2053,10 @@
       <c r="F35" s="1">
         <v>-5.49</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="K35" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="L35" s="4"/>
+      <c r="L35" s="19"/>
       <c r="M35" s="1">
         <v>-4.07</v>
       </c>
@@ -1859,7 +2073,7 @@
         <v>-3.98</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>2</v>
       </c>
@@ -1879,10 +2093,10 @@
       <c r="F36" s="1">
         <v>-2.36</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L36" s="6"/>
+      <c r="L36" s="3"/>
       <c r="M36" s="1">
         <v>-2.78</v>
       </c>
@@ -1899,7 +2113,7 @@
         <v>-2.61</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>3</v>
       </c>
@@ -1918,10 +2132,10 @@
       <c r="F37" s="1">
         <v>-5.83</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="K37" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="L37" s="4"/>
+      <c r="L37" s="19"/>
       <c r="M37" s="1">
         <v>-5.09</v>
       </c>
@@ -1938,7 +2152,7 @@
         <v>-5.0199999999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
@@ -1957,10 +2171,10 @@
       <c r="F38" s="1">
         <v>-4.84</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="K38" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="L38" s="4"/>
+      <c r="L38" s="19"/>
       <c r="M38" s="1">
         <v>-3.83</v>
       </c>
@@ -1977,7 +2191,7 @@
         <v>-3.66</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -1996,10 +2210,10 @@
       <c r="F39" s="1">
         <v>-5.01</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="K39" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="L39" s="4"/>
+      <c r="L39" s="19"/>
       <c r="M39" s="1">
         <v>-4.78</v>
       </c>
@@ -2016,8 +2230,8 @@
         <v>-4.62</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B40" s="1">
@@ -2029,16 +2243,17 @@
       <c r="D40" s="1">
         <v>-4.49</v>
       </c>
-      <c r="E40" s="27">
-        <v>1.31</v>
+      <c r="E40" s="13">
+        <f>AVERAGE(E35:E39)</f>
+        <v>0.52799999999999991</v>
       </c>
       <c r="F40" s="1">
         <v>-4.9800000000000004</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="K40" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="L40" s="4"/>
+      <c r="L40" s="19"/>
       <c r="M40" s="1">
         <v>-5.09</v>
       </c>
@@ -2049,40 +2264,41 @@
         <v>-3.91</v>
       </c>
       <c r="P40" s="1">
-        <v>0.81</v>
+        <f>AVERAGE(P35:P39)</f>
+        <v>0.18107999999999999</v>
       </c>
       <c r="Q40" s="1">
         <v>-3.97</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="22" t="s">
+      <c r="K41" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20" t="s">
+      <c r="L41" s="10"/>
+      <c r="M41" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N41" s="20" t="s">
+      <c r="N41" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O41" s="20" t="s">
+      <c r="O41" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
@@ -2095,10 +2311,10 @@
       <c r="D42" s="1">
         <v>0.79820000000000002</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K42" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="L42" s="2"/>
+      <c r="L42" s="24"/>
       <c r="M42" s="1">
         <v>256.62</v>
       </c>
@@ -2109,7 +2325,7 @@
         <v>0.79569999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>2</v>
       </c>
@@ -2122,10 +2338,10 @@
       <c r="D43" s="1">
         <v>0.90669999999999995</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="K43" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="L43" s="4"/>
+      <c r="L43" s="19"/>
       <c r="M43" s="1">
         <v>202.6</v>
       </c>
@@ -2136,7 +2352,7 @@
         <v>0.90939999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>3</v>
       </c>
@@ -2149,10 +2365,10 @@
       <c r="D44" s="1">
         <v>0.72899999999999998</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="K44" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="4"/>
+      <c r="L44" s="19"/>
       <c r="M44" s="1">
         <v>285.27</v>
       </c>
@@ -2163,7 +2379,7 @@
         <v>0.75029999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
@@ -2176,10 +2392,10 @@
       <c r="D45" s="1">
         <v>0.81769999999999998</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="K45" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="4"/>
+      <c r="L45" s="19"/>
       <c r="M45" s="1">
         <v>266.55</v>
       </c>
@@ -2190,7 +2406,7 @@
         <v>0.8135</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
@@ -2203,10 +2419,10 @@
       <c r="D46" s="1">
         <v>0.87590000000000001</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="K46" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="L46" s="4"/>
+      <c r="L46" s="19"/>
       <c r="M46" s="1">
         <v>227.17</v>
       </c>
@@ -2217,23 +2433,23 @@
         <v>0.87960000000000005</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K47" s="5" t="s">
+      <c r="K47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L47" s="6"/>
+      <c r="L47" s="3"/>
       <c r="M47" s="1" t="s">
         <v>31</v>
       </c>
@@ -2244,58 +2460,58 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="22" t="s">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H48" s="22" t="s">
+      <c r="H48" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K48" s="22" t="s">
+      <c r="K48" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20" t="s">
+      <c r="L48" s="10"/>
+      <c r="M48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N48" s="20" t="s">
+      <c r="N48" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O48" s="20" t="s">
+      <c r="O48" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P48" s="22" t="s">
+      <c r="P48" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="Q48" s="22" t="s">
+      <c r="Q48" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="R48" s="22" t="s">
+      <c r="R48" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="S48" s="22" t="s">
+      <c r="S48" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>1</v>
       </c>
@@ -2320,10 +2536,10 @@
       <c r="H49" s="1">
         <v>0.53</v>
       </c>
-      <c r="K49" s="9" t="s">
+      <c r="K49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L49" s="10"/>
+      <c r="L49" s="3"/>
       <c r="M49" s="1">
         <v>0.41199999999999998</v>
       </c>
@@ -2346,7 +2562,7 @@
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>2</v>
       </c>
@@ -2371,10 +2587,10 @@
       <c r="H50" s="1">
         <v>0.66800000000000004</v>
       </c>
-      <c r="K50" s="9" t="s">
+      <c r="K50" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L50" s="10"/>
+      <c r="L50" s="3"/>
       <c r="M50" s="1">
         <v>0.35299999999999998</v>
       </c>
@@ -2397,7 +2613,7 @@
         <v>0.65100000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>3</v>
       </c>
@@ -2422,10 +2638,10 @@
       <c r="H51" s="1">
         <v>0.70299999999999996</v>
       </c>
-      <c r="K51" s="9" t="s">
+      <c r="K51" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L51" s="10"/>
+      <c r="L51" s="3"/>
       <c r="M51" s="1">
         <v>0.54500000000000004</v>
       </c>
@@ -2448,7 +2664,7 @@
         <v>0.73799999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
@@ -2473,10 +2689,10 @@
       <c r="H52" s="1">
         <v>0.81499999999999995</v>
       </c>
-      <c r="K52" s="9" t="s">
+      <c r="K52" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="10"/>
+      <c r="L52" s="3"/>
       <c r="M52" s="1">
         <v>0.5</v>
       </c>
@@ -2499,7 +2715,7 @@
         <v>0.80400000000000005</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>5</v>
       </c>
@@ -2524,10 +2740,10 @@
       <c r="H53" s="1">
         <v>0.53500000000000003</v>
       </c>
-      <c r="K53" s="9" t="s">
+      <c r="K53" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L53" s="10"/>
+      <c r="L53" s="3"/>
       <c r="M53" s="1">
         <v>0.55900000000000005</v>
       </c>
@@ -2550,7 +2766,7 @@
         <v>0.54100000000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>17</v>
       </c>
@@ -2575,10 +2791,10 @@
       <c r="H54" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K54" s="9" t="s">
+      <c r="K54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L54" s="10"/>
+      <c r="L54" s="3"/>
       <c r="M54" s="1" t="s">
         <v>35</v>
       </c>
@@ -2601,38 +2817,66 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="20" t="s">
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="K57" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L57" s="20"/>
+      <c r="M57" s="20"/>
+      <c r="N57" s="20"/>
+      <c r="O57" s="20"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="20"/>
+      <c r="S57" s="4"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="B58" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E58" s="22" t="s">
+      <c r="E58" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F58" s="22" t="s">
+      <c r="F58" s="10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K58" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O58" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>1</v>
       </c>
@@ -2651,8 +2895,26 @@
       <c r="F59" s="1">
         <v>-5.33</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L59" s="1">
+        <v>-5.31</v>
+      </c>
+      <c r="M59" s="1">
+        <v>-4</v>
+      </c>
+      <c r="N59" s="1">
+        <v>-4.5</v>
+      </c>
+      <c r="O59" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="P59" s="1">
+        <v>-4.49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>2</v>
       </c>
@@ -2671,8 +2933,26 @@
       <c r="F60" s="1">
         <v>-3.48</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L60" s="1">
+        <v>-3.35</v>
+      </c>
+      <c r="M60" s="1">
+        <v>-2.1</v>
+      </c>
+      <c r="N60" s="1">
+        <v>-2.89</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P60" s="1">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
@@ -2691,8 +2971,26 @@
       <c r="F61" s="1">
         <v>-4.74</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L61" s="1">
+        <v>-5.75</v>
+      </c>
+      <c r="M61" s="1">
+        <v>-5.43</v>
+      </c>
+      <c r="N61" s="1">
+        <v>-5.62</v>
+      </c>
+      <c r="O61" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="P61" s="1">
+        <v>-5.61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>4</v>
       </c>
@@ -2711,8 +3009,26 @@
       <c r="F62" s="1">
         <v>-4.1900000000000004</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="1">
+        <v>-5.73</v>
+      </c>
+      <c r="M62" s="1">
+        <v>-3.64</v>
+      </c>
+      <c r="N62" s="1">
+        <v>-4.43</v>
+      </c>
+      <c r="O62" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="P62" s="1">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -2731,9 +3047,27 @@
       <c r="F63" s="1">
         <v>-5.0999999999999996</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="K63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L63" s="1">
+        <v>-5.09</v>
+      </c>
+      <c r="M63" s="1">
+        <v>-4.03</v>
+      </c>
+      <c r="N63" s="1">
+        <v>-4.42</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="P63" s="1">
+        <v>-4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B64" s="1">
@@ -2746,27 +3080,60 @@
         <v>-4.5999999999999996</v>
       </c>
       <c r="E64" s="1">
-        <v>1.17</v>
+        <f>AVERAGE(E59:E63)</f>
+        <v>0.92199999999999993</v>
       </c>
       <c r="F64" s="1">
         <v>-4.57</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="22" t="s">
+      <c r="K64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="1">
+        <v>-5.75</v>
+      </c>
+      <c r="M64" s="1">
+        <v>-2.1</v>
+      </c>
+      <c r="N64" s="1">
+        <f>AVERAGE(N59:N63)</f>
+        <v>-4.3719999999999999</v>
+      </c>
+      <c r="O64" s="13">
+        <f>AVERAGE(O59:O63)</f>
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="P64" s="1">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K65" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>1</v>
       </c>
@@ -2779,8 +3146,20 @@
       <c r="D66" s="1">
         <v>0.78820000000000001</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1">
+        <v>258.64</v>
+      </c>
+      <c r="M66" s="1">
+        <v>356.04</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0.80069999999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>2</v>
       </c>
@@ -2793,8 +3172,20 @@
       <c r="D67" s="1">
         <v>0.91410000000000002</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L67" s="1">
+        <v>196.88</v>
+      </c>
+      <c r="M67" s="1">
+        <v>271.58999999999997</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0.91300000000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -2807,8 +3198,20 @@
       <c r="D68" s="1">
         <v>0.747</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L68" s="1">
+        <v>311.2</v>
+      </c>
+      <c r="M68" s="1">
+        <v>410.73</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0.72629999999999995</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>4</v>
       </c>
@@ -2821,8 +3224,20 @@
       <c r="D69" s="1">
         <v>0.83560000000000001</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L69" s="1">
+        <v>249.4</v>
+      </c>
+      <c r="M69" s="1">
+        <v>329.21</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0.82909999999999995</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -2835,9 +3250,21 @@
       <c r="D70" s="1">
         <v>0.87819999999999998</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="K70" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L70" s="1">
+        <v>229.17</v>
+      </c>
+      <c r="M70" s="1">
+        <v>306.25</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0.876</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -2849,34 +3276,70 @@
       <c r="D71" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="22" t="s">
+      <c r="K71" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A72" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D72" s="20" t="s">
+      <c r="D72" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F72" s="22" t="s">
+      <c r="F72" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G72" s="22" t="s">
+      <c r="G72" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H72" s="22" t="s">
+      <c r="H72" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K72" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O72" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q72" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R72" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>1</v>
       </c>
@@ -2901,8 +3364,32 @@
       <c r="H73" s="1">
         <v>0.52500000000000002</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="M73" s="1">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="O73" s="1">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="P73" s="1">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0.50900000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>2</v>
       </c>
@@ -2927,8 +3414,32 @@
       <c r="H74" s="1">
         <v>0.70599999999999996</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K74" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="M74" s="1">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="N74" s="1">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="O74" s="1">
+        <v>0.154</v>
+      </c>
+      <c r="P74" s="1">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>0.443</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0.66600000000000004</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -2953,8 +3464,32 @@
       <c r="H75" s="1">
         <v>0.72599999999999998</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="O75" s="1">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="P75" s="1">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0.72599999999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>4</v>
       </c>
@@ -2979,8 +3514,32 @@
       <c r="H76" s="1">
         <v>0.79100000000000004</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="M76" s="1">
+        <v>1</v>
+      </c>
+      <c r="N76" s="1">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="O76" s="1">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="P76" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="R76" s="1">
+        <v>0.85799999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>5</v>
       </c>
@@ -3005,8 +3564,32 @@
       <c r="H77" s="1">
         <v>0.51800000000000002</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K77" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L77" s="1">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="M77" s="1">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="N77" s="1">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="O77" s="1">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P77" s="1">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="R77" s="1">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>17</v>
       </c>
@@ -3031,14 +3614,474 @@
       <c r="H78" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="K78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P78" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B84" s="1">
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="C84" s="1">
+        <v>-4.8600000000000003</v>
+      </c>
+      <c r="D84" s="1">
+        <v>-5.05</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F84" s="1">
+        <v>-5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" s="1">
+        <v>-3.03</v>
+      </c>
+      <c r="C85" s="1">
+        <v>-2.79</v>
+      </c>
+      <c r="D85" s="1">
+        <v>-2.91</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F85" s="1">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="1">
+        <v>-6.16</v>
+      </c>
+      <c r="C86" s="1">
+        <v>-2.52</v>
+      </c>
+      <c r="D86" s="1">
+        <v>-5.42</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="F86" s="1">
+        <v>-6.06</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="1">
+        <v>-4.82</v>
+      </c>
+      <c r="C87" s="1">
+        <v>-2.86</v>
+      </c>
+      <c r="D87" s="1">
+        <v>-4.3899999999999997</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="F87" s="1">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" s="1">
+        <v>-4.75</v>
+      </c>
+      <c r="C88" s="1">
+        <v>-4.54</v>
+      </c>
+      <c r="D88" s="1">
+        <v>-4.68</v>
+      </c>
+      <c r="E88" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F88" s="1">
+        <v>-4.71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B89" s="1">
+        <v>-6.16</v>
+      </c>
+      <c r="C89" s="1">
+        <v>-2.52</v>
+      </c>
+      <c r="D89" s="1">
+        <v>-4.49</v>
+      </c>
+      <c r="E89" s="1">
+        <f>AVERAGE(E84:E88)</f>
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="F89" s="1">
+        <f>-4.72</f>
+        <v>-4.72</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B91" s="1">
+        <v>270.68</v>
+      </c>
+      <c r="C91" s="1">
+        <v>362.79</v>
+      </c>
+      <c r="D91" s="1">
+        <v>0.79310000000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" s="1">
+        <v>197.04</v>
+      </c>
+      <c r="C92" s="1">
+        <v>270.07</v>
+      </c>
+      <c r="D92" s="1">
+        <v>0.91400000000000003</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="1">
+        <v>291.31</v>
+      </c>
+      <c r="C93" s="1">
+        <v>401.45</v>
+      </c>
+      <c r="D93" s="1">
+        <v>0.73850000000000005</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" s="1">
+        <v>256.77999999999997</v>
+      </c>
+      <c r="C94" s="1">
+        <v>330.38</v>
+      </c>
+      <c r="D94" s="1">
+        <v>0.82789999999999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="1">
+        <v>230.49</v>
+      </c>
+      <c r="C95" s="1">
+        <v>304.95999999999998</v>
+      </c>
+      <c r="D95" s="1">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B98" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="D98" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B99" s="1">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E99" s="1">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F99" s="1">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0.67100000000000004</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="1">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0.68200000000000005</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" s="1">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="F101" s="1">
+        <v>1</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" s="1">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="D102" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="E102" s="1">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0.54600000000000004</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="A57:G57"/>
+  <mergeCells count="21">
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K38:L38"/>
     <mergeCell ref="K33:R33"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A7:F7"/>
@@ -3046,14 +4089,14 @@
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="K57:Q57"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/Comparisons.xlsx
+++ b/Comparisons.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FrancescoP\ImagingBased-ProgressionPrediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29733014-D1E7-4152-B626-3C1CA529FD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EEE758-675E-4FBD-AD58-4020C5FD0855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2EE0F8F3-7531-4A73-A202-515B415B47BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables_comparison" sheetId="1" r:id="rId1"/>
+    <sheet name="CNN_Corrected" sheetId="2" r:id="rId2"/>
+    <sheet name="FVC@52 Predictor" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="160">
   <si>
     <t>Slope distribution</t>
   </si>
@@ -324,6 +326,198 @@
   </si>
   <si>
     <t>MAE FVC(52)</t>
+  </si>
+  <si>
+    <t>CNN+Demographics</t>
+  </si>
+  <si>
+    <t>CNN+Handcrafted</t>
+  </si>
+  <si>
+    <t>CNN+Demographics+Handcrafted</t>
+  </si>
+  <si>
+    <t>0.512 ± 0.078</t>
+  </si>
+  <si>
+    <t>0.673 ± 0.145</t>
+  </si>
+  <si>
+    <t>0.406 ± 0.153</t>
+  </si>
+  <si>
+    <t>0.471 ± 0.134</t>
+  </si>
+  <si>
+    <t>0.581 ± 0.086</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.655 ± 0.117</t>
+  </si>
+  <si>
+    <t>0.526 ± 0.084</t>
+  </si>
+  <si>
+    <t>0.709 ± 0.180</t>
+  </si>
+  <si>
+    <t>0.407 ± 0.151</t>
+  </si>
+  <si>
+    <t>0.480 ± 0.133</t>
+  </si>
+  <si>
+    <t>0.721 ± 0.210</t>
+  </si>
+  <si>
+    <t>0.593 ± 0.085</t>
+  </si>
+  <si>
+    <t>0.667 ± 0.115</t>
+  </si>
+  <si>
+    <t>0.533 ± 0.093</t>
+  </si>
+  <si>
+    <t>0.716 ± 0.182</t>
+  </si>
+  <si>
+    <t>0.410 ± 0.142</t>
+  </si>
+  <si>
+    <t>0.488 ± 0.135</t>
+  </si>
+  <si>
+    <t>0.739 ± 0.206</t>
+  </si>
+  <si>
+    <t>0.585 ± 0.067</t>
+  </si>
+  <si>
+    <t>0.664 ± 0.107</t>
+  </si>
+  <si>
+    <t>Comparison</t>
+  </si>
+  <si>
+    <t>CNN only</t>
+  </si>
+  <si>
+    <t>Prediction with deltaFVC</t>
+  </si>
+  <si>
+    <t>Fold</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>0.473 ± 0.024</t>
+  </si>
+  <si>
+    <t>0.569 ± 0.146</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.384 ± 0.125</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.445 ± 0.113</t>
+  </si>
+  <si>
+    <t>0.600 ± 0.140</t>
+  </si>
+  <si>
+    <t>0.505 ± 0.094</t>
+  </si>
+  <si>
+    <t>0.591 ± 0.115</t>
+  </si>
+  <si>
+    <t>Direct Prediction</t>
+  </si>
+  <si>
+    <t>0.478 ± 0.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.550 ± 0.191</t>
+  </si>
+  <si>
+    <t>0.386 ± 0.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.448 ± 0.157</t>
+  </si>
+  <si>
+    <t>0.597 ± 0.150</t>
+  </si>
+  <si>
+    <t>0.483 ± 0.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.582 ± 0.129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method </t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>Dual</t>
+  </si>
+  <si>
+    <t>========================================================================</t>
+  </si>
+  <si>
+    <t>AGGREGATE RESULTS</t>
+  </si>
+  <si>
+    <t>================================================================================</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fold  N  Prog Accuracy Precision Recall    F1 Specificity   AUC    AP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    0 36    18    0.528     0.526  0.556 0.541       0.500 0.546 0.527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1 35    24    0.686     0.686  1.000 0.814       0.000 0.479 0.677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2 35    23    0.343     0.000  0.000 0.000       1.000 0.457 0.704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3 35    21    0.400     0.000  0.000 0.000       1.000 0.449 0.607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4 35    18    0.486     0.000  0.000 0.000       1.000 0.660 0.614</t>
+  </si>
+  <si>
+    <t>============================================================</t>
+  </si>
+  <si>
+    <t>MEAN ± STD ACROSS FOLDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Accuracy       : 0.488 ± 0.118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Precision      : 0.242 ± 0.301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Recall         : 0.311 ± 0.406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  F1 Score       : 0.271 ± 0.343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Specificity    : 0.700 ± 0.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Auc Roc        : 0.518 ± 0.079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Average Precision: 0.626 ± 0.062</t>
   </si>
 </sst>
 </file>
@@ -495,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -516,38 +710,67 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -556,6 +779,298 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -574,110 +1089,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1026,19 +1437,310 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>58207</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>119744</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>209796</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>24333</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E6E2812-3274-4FD4-908A-BA20B2EAE4E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10682664" y="1045030"/>
+          <a:ext cx="2589989" cy="2125274"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>65314</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>147573</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D8CF597-538D-0900-C883-D711F341E5BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10232571" y="6106887"/>
+          <a:ext cx="2520659" cy="1872342"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>32657</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>195943</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>109894</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F357E61F-C7B3-E435-9C7E-1D9CF96DD622}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10199914" y="4049486"/>
+          <a:ext cx="2601686" cy="1982237"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>65316</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>217716</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>82356</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FA613A7-4A59-8415-DF1F-EA9106146C35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10243457" y="8207830"/>
+          <a:ext cx="2579916" cy="1682555"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533399</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>274318</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>163152</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C08683B-C168-A865-CC67-D09DEDDC3277}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7703819" y="2926080"/>
+          <a:ext cx="2179319" cy="1626192"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>515046</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>190497</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C5A8B2E-B96E-75EA-A4AC-5A2AD3B56894}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7685466" y="1120140"/>
+          <a:ext cx="2113851" cy="1577340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3DAEFBCC-FF40-4F66-B649-0C96AC862806}" name="Table2" displayName="Table2" ref="A25:I30" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3DAEFBCC-FF40-4F66-B649-0C96AC862806}" name="Table2" displayName="Table2" ref="A25:I30" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A25:I30" xr:uid="{3DAEFBCC-FF40-4F66-B649-0C96AC862806}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1AB4FC38-4517-44F4-A99A-E57AA670AD0F}" name="Training" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{B424091A-0662-4390-A0BE-918C2A0A03FC}" name="Accuracy" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{EB3FD60A-926F-457D-B1BB-C6AA1875C8C0}" name="Precision" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{DD322310-0117-4984-99C0-4E835D410D91}" name="Recall" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{E019C0FD-7F71-4FCD-A98E-66D99246B5AB}" name="F1-Score" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{DC66C15B-74CC-4F2B-858F-2B2AA38304B0}" name="Specificity" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{1AB4FC38-4517-44F4-A99A-E57AA670AD0F}" name="Training" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{B424091A-0662-4390-A0BE-918C2A0A03FC}" name="Accuracy" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{EB3FD60A-926F-457D-B1BB-C6AA1875C8C0}" name="Precision" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{DD322310-0117-4984-99C0-4E835D410D91}" name="Recall" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{E019C0FD-7F71-4FCD-A98E-66D99246B5AB}" name="F1-Score" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{DC66C15B-74CC-4F2B-858F-2B2AA38304B0}" name="Specificity" dataDxfId="14"/>
     <tableColumn id="8" xr3:uid="{47AE70D0-AB50-4496-AFB0-1AD3D4827CA8}" name="AUC"/>
-    <tableColumn id="9" xr3:uid="{45ADE258-6CA2-422A-81B2-1753A5D5207C}" name="AP" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{2E69A242-1017-4CBC-88EB-F049FD853CEF}" name="MAE FVC(52)" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{45ADE258-6CA2-422A-81B2-1753A5D5207C}" name="AP" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{2E69A242-1017-4CBC-88EB-F049FD853CEF}" name="MAE FVC(52)" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{283C3EB8-5609-4992-9DA2-D096A2931B4C}" name="Table4" displayName="Table4" ref="B54:I58" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+  <autoFilter ref="B54:I58" xr:uid="{283C3EB8-5609-4992-9DA2-D096A2931B4C}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{3804F7FF-3518-4004-8801-5F48A60B7575}" name="Comparison" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{BFD40A82-7234-4E43-ADB0-D7E21511D420}" name="Accuracy" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{31955317-14D4-482F-A780-7A369586C696}" name="Precision" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{3FFDF15D-F4FF-4C1F-846A-06C62F1F7346}" name="Recall" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{72BAAF2B-6ABC-45E4-9DEA-BDB382A0A91E}" name="F1-Score" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{95764A1F-BE38-4B5A-A259-F10FA2320A2F}" name="Specificity" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4E089CA8-B016-4BF2-A76C-F4F63C6E73B7}" name="AUC" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{94336788-43C2-49A6-B63A-CE34E81BA464}" name="AP" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1424,14 +2126,14 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1494,14 +2196,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="23"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1564,14 +2266,14 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1634,14 +2336,14 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -1704,14 +2406,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="27"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1774,17 +2476,17 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
@@ -1811,14 +2513,14 @@
       <c r="H25" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="27" t="s">
+      <c r="I25" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="19" t="s">
         <v>68</v>
       </c>
       <c r="B26" s="10" t="s">
@@ -1845,11 +2547,9 @@
       <c r="I26" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="19" t="s">
         <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1876,11 +2576,9 @@
       <c r="I27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="20" t="s">
         <v>81</v>
       </c>
       <c r="B28" s="5" t="s">
@@ -1895,7 +2593,7 @@
       <c r="E28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="5" t="s">
         <v>39</v>
       </c>
       <c r="G28" s="5" t="s">
@@ -1907,11 +2605,9 @@
       <c r="I28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="20" t="s">
         <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1938,11 +2634,9 @@
       <c r="I29" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -1969,31 +2663,29 @@
       <c r="I30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="20" t="s">
+      <c r="K33" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
@@ -2053,10 +2745,10 @@
       <c r="F35" s="1">
         <v>-5.49</v>
       </c>
-      <c r="K35" s="18" t="s">
+      <c r="K35" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="L35" s="19"/>
+      <c r="L35" s="23"/>
       <c r="M35" s="1">
         <v>-4.07</v>
       </c>
@@ -2132,10 +2824,10 @@
       <c r="F37" s="1">
         <v>-5.83</v>
       </c>
-      <c r="K37" s="18" t="s">
+      <c r="K37" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="L37" s="19"/>
+      <c r="L37" s="23"/>
       <c r="M37" s="1">
         <v>-5.09</v>
       </c>
@@ -2171,10 +2863,10 @@
       <c r="F38" s="1">
         <v>-4.84</v>
       </c>
-      <c r="K38" s="18" t="s">
+      <c r="K38" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L38" s="19"/>
+      <c r="L38" s="23"/>
       <c r="M38" s="1">
         <v>-3.83</v>
       </c>
@@ -2210,10 +2902,10 @@
       <c r="F39" s="1">
         <v>-5.01</v>
       </c>
-      <c r="K39" s="18" t="s">
+      <c r="K39" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="L39" s="19"/>
+      <c r="L39" s="23"/>
       <c r="M39" s="1">
         <v>-4.78</v>
       </c>
@@ -2250,10 +2942,10 @@
       <c r="F40" s="1">
         <v>-4.9800000000000004</v>
       </c>
-      <c r="K40" s="18" t="s">
+      <c r="K40" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="L40" s="19"/>
+      <c r="L40" s="23"/>
       <c r="M40" s="1">
         <v>-5.09</v>
       </c>
@@ -2338,10 +3030,10 @@
       <c r="D43" s="1">
         <v>0.90669999999999995</v>
       </c>
-      <c r="K43" s="18" t="s">
+      <c r="K43" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="L43" s="19"/>
+      <c r="L43" s="23"/>
       <c r="M43" s="1">
         <v>202.6</v>
       </c>
@@ -2365,10 +3057,10 @@
       <c r="D44" s="1">
         <v>0.72899999999999998</v>
       </c>
-      <c r="K44" s="18" t="s">
+      <c r="K44" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="19"/>
+      <c r="L44" s="23"/>
       <c r="M44" s="1">
         <v>285.27</v>
       </c>
@@ -2392,10 +3084,10 @@
       <c r="D45" s="1">
         <v>0.81769999999999998</v>
       </c>
-      <c r="K45" s="18" t="s">
+      <c r="K45" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="19"/>
+      <c r="L45" s="23"/>
       <c r="M45" s="1">
         <v>266.55</v>
       </c>
@@ -2419,10 +3111,10 @@
       <c r="D46" s="1">
         <v>0.87590000000000001</v>
       </c>
-      <c r="K46" s="18" t="s">
+      <c r="K46" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="L46" s="19"/>
+      <c r="L46" s="23"/>
       <c r="M46" s="1">
         <v>227.17</v>
       </c>
@@ -2818,24 +3510,24 @@
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="K57" s="20" t="s">
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="K57" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="20"/>
-      <c r="O57" s="20"/>
-      <c r="P57" s="20"/>
-      <c r="Q57" s="20"/>
+      <c r="L57" s="21"/>
+      <c r="M57" s="21"/>
+      <c r="N57" s="21"/>
+      <c r="O57" s="21"/>
+      <c r="P57" s="21"/>
+      <c r="Q57" s="21"/>
       <c r="S57" s="4"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
@@ -3640,15 +4332,15 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
@@ -4074,6 +4766,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="K42:L42"/>
@@ -4083,16 +4785,6 @@
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="K38:L38"/>
     <mergeCell ref="K33:R33"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="K46:L46"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="K57:Q57"/>
   </mergeCells>
@@ -4104,4 +4796,1671 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E0F9A6-A82E-44D6-9E72-8A522ADEFE04}">
+  <dimension ref="B5:I59"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" customWidth="1"/>
+    <col min="4" max="4" width="18.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-7.74</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-3.33</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-5.36</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-5.33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-4.8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-2.17</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-4.4800000000000004</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="G8" s="1">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>-7.06</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-3.35</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-4.8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="G9" s="1">
+        <v>-4.74</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1">
+        <v>-7.96</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-2.08</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-4.32</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1.38</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-4.1900000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-6.32</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-3.54</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-5.0199999999999996</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1">
+        <v>-7.96</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-2.08</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="F12" s="1">
+        <f>AVERAGE(F7:F11)</f>
+        <v>0.92199999999999993</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-4.57</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>278.81</v>
+      </c>
+      <c r="D14" s="1">
+        <v>367.05</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.78820000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>195.24</v>
+      </c>
+      <c r="D15" s="1">
+        <v>269.94</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.91410000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
+        <v>279.66000000000003</v>
+      </c>
+      <c r="D16" s="1">
+        <v>394.92</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.747</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1">
+        <v>253.94</v>
+      </c>
+      <c r="D17" s="1">
+        <v>322.87</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.83560000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1">
+        <v>233.74</v>
+      </c>
+      <c r="D18" s="1">
+        <v>303.45</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.87819999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.222</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.496</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.70599999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0.72599999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0.79100000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.502</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0.51800000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="27"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0.51200000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0.222</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0.71399999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0.74099999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0.79100000000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.502</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0.51800000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="30"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0.51300000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0.68400000000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0.73699999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0.83099999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.56899999999999995</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H40" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="30"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0.69199999999999995</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0.79600000000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0.57299999999999995</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B54" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B55" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B56" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B58" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I58" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B59" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B41:I41"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8A0A52-CD85-4292-9784-F5185C912A5C}">
+  <dimension ref="A2:H48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="C9">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="D9">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="E9">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="G9">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="H9">
+        <v>0.45100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="C10">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="D10">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="E10">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="F10">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="G10">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="H10">
+        <v>0.79700000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="C11">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="D11">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="E11">
+        <v>0.5</v>
+      </c>
+      <c r="F11">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="G11">
+        <v>0.5</v>
+      </c>
+      <c r="H11">
+        <v>0.65900000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>0.433</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="E12">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="H12">
+        <v>0.51800000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="C13">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="D13">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="E13">
+        <v>0.438</v>
+      </c>
+      <c r="F13">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="G13">
+        <v>0.436</v>
+      </c>
+      <c r="H13">
+        <v>0.48599999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G14" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <v>0.441</v>
+      </c>
+      <c r="C19">
+        <v>0.375</v>
+      </c>
+      <c r="D19">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="E19">
+        <v>0.24</v>
+      </c>
+      <c r="F19">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="G19">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="H19">
+        <v>0.46700000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="C20">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="D20">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="E20">
+        <v>0.438</v>
+      </c>
+      <c r="F20">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="G20">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="H20">
+        <v>0.751</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="C21">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="D21">
+        <v>0.5</v>
+      </c>
+      <c r="E21">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="F21">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="G21">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="H21">
+        <v>0.70099999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="C22">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="D22">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+      <c r="F22">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="G22">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="H22">
+        <v>0.55100000000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="C23">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="D23">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="E23">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="F23">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="G23">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="H23">
+        <v>0.48599999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>